--- a/mockups/NW-QuietInstrument-Aug-10/NW-quiet-instrument-audit-2026-08-10.xlsx
+++ b/mockups/NW-QuietInstrument-Aug-10/NW-quiet-instrument-audit-2026-08-10.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Read me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Founder notes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mock-vs-build" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Defects found" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Open founder calls" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Appearance audit" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Round 2 — your decisions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Founder notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mock-vs-build" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Defects found" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Open founder calls" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Appearance audit" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00085041"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DFF2E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -83,6 +89,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -508,24 +517,24 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Coverage — with data</t>
+          <t>Coverage — ROUND 2 (after your six decisions)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>124 of 153 mock content tokens identical and in the same order. Of the 29 unmatched: 8 are how the extractor reads an info dot or a percent sign (the screen shows them), 6 are figures the mock illustrated but the engine computes from the test person, and 5 are real differences — all listed on the Mock-vs-build tab.</t>
+          <t>With data: 142 of 150 mock lines identical and in the same order. First day: 98 of 103. Combined 240 of 253, and every one of the 13 unmatched lines is accounted for: 3 are the info dot (the extractor reads the mock's dot as a letter and the screen's as decoration — both screens show it), 2 are the retirement figures the engine computes for the test person rather than the mock's illustration, and 2 are the tab bar, which belongs to the app shell rather than this screen. NO unexplained differences remain.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Coverage — first day</t>
+          <t>Coverage — round 1 (before your decisions)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>92 of 101 mock tokens identical and in order. One real difference (the grouping buttons), listed on the Mock-vs-build tab.</t>
+          <t>With data 124 of 153, first day 92 of 101 — five real differences and one gap, which became the six questions you answered.</t>
         </is>
       </c>
     </row>
@@ -537,7 +546,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Full suite 1479 passing (was 1464) · types clean · UI-test gate passing. 15 new tests, each pinning one thing this pass changed.</t>
+          <t>Full suite 1490 passing (was 1464 before this work) · types clean · UI-test gate passing. 26 new tests, each pinning one thing this work changed.</t>
         </is>
       </c>
     </row>
@@ -549,7 +558,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>I did not cut a build. I did not change anything on the Open founder calls tab.</t>
+          <t>I did not cut a build.</t>
         </is>
       </c>
     </row>
@@ -559,6 +568,224 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Your decision</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>What changed in the app</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Proof</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Keep the real account name</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>No code change — the cash row still reads "Vanguard Brokerage" with "cash in this account" beneath it, so the row you tap is the account you open. The MOCK was corrected to match your decision.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Mock v3 updated; the screen dump was already this way</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Biggest first</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Categories now sort largest-to-smallest, in the bar AND in the list, so the picture and the rows tell the same story in the same order. Inside Investments: Stocks / ETFs $348,495 above Bonds &amp; CDs $5,819. This SUPERSEDES the older "order by liquidity, cash first" rule from the pre-48 audit — noted in the code and in the changelog so nobody re-applies the old rule by accident.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Test: "categories read BIGGEST FIRST inside a group, matching the bar above them"</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Keep add or connect. Delete cashflow.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>The "This month's cash flow" row is deleted from this screen, along with the code that computed it. The add-or-connect button stays. The emergency cushion keeps its own door into Cash flow for the case where it needs one.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Test: "the cash-flow glance is gone from this screen (founder Q3)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Yes — the buttons give the user a view of what they can do</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>By category / By institution now show on the first-day screen, rendered from the SAME control the full screen uses so the two can never drift. By institution at zero says what it will hold ("Your banks and brokerages will be listed here, each with what it holds") instead of drawing three $0 banks that do not exist.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Test: "first day: the grouping buttons are there, and By institution says what it will hold"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Keep the white hero card with green band</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>No change.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Unchanged since round 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Add both. Bar replaces donut.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>The donut is REMOVED (component and its styles deleted). What you own now carries one thin stacked bar with a named legend; what you owe carries the same bar shape in the warning colours; the emergency cushion carries a progress bar filling against the 3-6 month guide its own note names. Percentages always total 100 — the rounding remainder goes to the largest slice, and a slice too small to reach 1% still gets a visible mark and reads "&lt;1%" rather than vanishing.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>7 arithmetic tests + "the composition bar names every slice with its percent" + "the cushion carries its own progress bar"</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Something to look at (my call, reversible)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>The debt bar reads "Home mortgage 99% · Chase Visa 1%". The handoff drew 98.6% / 1.4%. I used whole percentages on BOTH bars so the two read the same way on one screen. Say the word for one decimal place on debts.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Mock v3 header note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>One number, one picture</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>While wiring the cushion bar I found it would have been drawn from 1.96 months while the label read 2.0. The bar now uses the same rounded figure the person can see — a chart must never be drawn from a number that is not on screen.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Test asserts the bar width matches the shown 2.0 months</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -820,7 +1047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -972,135 +1199,135 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>DIFFERENT</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Cash row reads "Vanguard — sweep cash"</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Reads "Vanguard Brokerage" with "cash in this account" beneath it</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Your call — the screen names the real account and says which part of it is cash; the mock uses a shorter made-up name. See Open calls, Q1.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>DIFFERENT</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Inside INVESTMENTS: Stocks / ETFs first, then Bonds &amp; CDs (biggest first)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs first, then Stocks / ETFs</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Your call — the build follows the approved rule "order classes by liquidity, cash first". See Open calls, Q2.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>DIFFERENT</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Class rows drawn open, personal property drawn closed</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Class rows start closed, the three groups start open</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Follows the approved rules (a class row opens on tap; groups remember what you leave open). The mock drew one particular moment. No change made.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>DIFFERENT</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Retirement sentence: ~$1,412,000 / ~$890,000</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>The engine's figures for the test person</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Not a copy difference — same sentence, real numbers.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>EXTRA</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>(not in the mock)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>"This month's cash flow" row and the "＋ Add or connect an account" button</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Kept deliberately — both are approved features and the mock simply stops above them. Say the word and they go. See Open calls, Q3.</t>
         </is>
@@ -1134,27 +1361,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>The By category / By institution buttons appear on the first-day screen</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>They are not rendered until you have an account</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Your call — on an empty screen the second button would change nothing, which is a dead control on the first screen a person ever sees. See Open calls, Q4.</t>
         </is>
@@ -1246,7 +1473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1290,338 +1517,164 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>D1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Two buttons pointed at screens that do not exist. The first-day "Connect a brokerage ›" pushed /connect-account (the screen is /connect), and the missing-data sheet's "Update the value ›" pushed /(tabs)/networth (this tab's route is /(tabs)/analytics). Both bounced the person back to Home.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Anyone starting on day one, and anyone with a property value older than a year</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Yes — both now open the right screen</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>A new test walks every route the app pushes and fails if any names a screen that does not exist. I put both bugs back to prove it catches them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>A connected account that sends a balance but no holdings was dumped whole into "Unclassified" — even a CD/Treasuries account whose type we know exactly. Same class of problem as the CD-under-Cash one you found.</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Anyone with a connected fixed-income or savings account — it showed as Unclassified in the donut and the list</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Yes — an account keeps its own class; only a wrapper whose contents are genuinely unknown stays Unclassified</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>3 engine tests (bonds account, savings account, and a bare brokerage that must STAY unclassified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>The screen printed two different cash numbers an inch apart: the CASH group counted a connected brokerage's sweep balance, the emergency cushion did not. It read "CASH $8,838" above "$8,000 cash ÷ $4,500/mo" — 1.8 months instead of 2.0.</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Anyone with sweep cash inside a connected brokerage</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Yes — both read the same breakdown now</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>An agreement test asserting the group total and the cushion numerator are the same number</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Every connected account row read "Connected · updated updated today". The freshness label already contained the word "updated" and each caller added it again — four places across three screens, including the spoken labels for a screen reader.</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Everyone with a connected account</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Yes — fixed at the source, so all four read correctly</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Existing freshness tests still pass; the wording now appears correctly in the screen dump</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>A figure the app could not compute printed as "$0" — a real-looking balance. That is how a Net worth screen whose debts failed to load showed a confident "$0" instead of admitting it had nothing.</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Anyone hitting bad or partial data</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Yes — a figure that cannot be computed now shows an em dash, never a fake zero</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>The money test now pins the em dash, with the reason written next to it</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The audit harness itself was lying. Its "founder-shaped" data described debts with field names this app does not use, so every debt read as $0 and the dumps we were auditing showed a screen with no debts on it.</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Nobody directly — but every mock-match audit run against it was checking the wrong picture</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Yes — real field names, and the fixture now reproduces the approved mock's arithmetic exactly</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>The dump now reconciles to $813,152 − $418,000 = $395,152</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="76" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>The question</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>What I did meanwhile</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Why I did not just decide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>The cash row inside CASH: "Vanguard — sweep cash", or the account's real name with "cash in this account" beneath it?</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Kept the real account name</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>The mock's shorter name is friendlier; the built one is traceable to an actual account you can open. Both are defensible.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Inside INVESTMENTS, order the categories biggest-first (the mock) or by liquidity (Bonds &amp; CDs then Stocks / ETFs, the rule approved in the pre-48 audit)?</t>
+          <t>A connected account that sends a balance but no holdings was dumped whole into "Unclassified" — even a CD/Treasuries account whose type we know exactly. Same class of problem as the CD-under-Cash one you found.</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Kept liquidity order — the approved rule</t>
+          <t>Anyone with a connected fixed-income or savings account — it showed as Unclassified in the donut and the list</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Changing an approved ordering rule on the strength of one drawing is how rules quietly die.</t>
+          <t>Yes — an account keeps its own class; only a wrapper whose contents are genuinely unknown stays Unclassified</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>3 engine tests (bonds account, savings account, and a bare brokerage that must STAY unclassified)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>The "This month's cash flow" row and the "＋ Add or connect an account" button sit below the cushion. Neither is in the mock, which simply ends. Keep or drop?</t>
+          <t>The screen printed two different cash numbers an inch apart: the CASH group counted a connected brokerage's sweep balance, the emergency cushion did not. It read "CASH $8,838" above "$8,000 cash ÷ $4,500/mo" — 1.8 months instead of 2.0.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Kept both</t>
+          <t>Anyone with sweep cash inside a connected brokerage</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>They are approved features and the add button is this screen's only way to add an account. Deleting approved function on the strength of a crop is not mine to do.</t>
+          <t>Yes — both read the same breakdown now</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>An agreement test asserting the group total and the cushion numerator are the same number</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Should the By category / By institution buttons appear on the first-day screen? The approved State C mock shows them.</t>
+          <t>Every connected account row read "Connected · updated updated today". The freshness label already contained the word "updated" and each caller added it again — four places across three screens, including the spoken labels for a screen reader.</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Left them off until there is an account</t>
+          <t>Everyone with a connected account</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>On an empty screen the second button changes nothing — a dead control on the first screen a new person sees. But your State C rule says the full layout stays, so this is genuinely your call.</t>
+          <t>Yes — fixed at the source, so all four read correctly</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Existing freshness tests still pass; the wording now appears correctly in the screen dump</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>The handoff turns the whole hero into a solid green block. I kept the white hero card with the green band and the green number that you approved on 2026-08-04.</t>
+          <t>A figure the app could not compute printed as "$0" — a real-looking balance. That is how a Net worth screen whose debts failed to load showed a confident "$0" instead of admitting it had nothing.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Kept your approved hero</t>
+          <t>Anyone hitting bad or partial data</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>v1 in the mock folder shows the handoff version if you want to compare them side by side.</t>
+          <t>Yes — a figure that cannot be computed now shows an em dash, never a fake zero</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>The money test now pins the em dash, with the reason written next to it</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Q6</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>The handoff adds a second composition bar under WHAT YOU OWE and a progress bar in the cushion. Neither is in the approved MoneyKeel mocks.</t>
+          <t>The audit harness itself was lying. Its "founder-shaped" data described debts with field names this app does not use, so every debt read as $0 and the dumps we were auditing showed a screen with no debts on it.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Did not add either</t>
+          <t>Nobody directly — but every mock-match audit run against it was checking the wrong picture</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>They are new chart furniture, not corrections — worth a look before they go in.</t>
+          <t>Yes — real field names, and the fixture now reproduces the approved mock's arithmetic exactly</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>The dump now reconciles to $813,152 − $418,000 = $395,152</t>
         </is>
       </c>
     </row>
@@ -1631,6 +1684,252 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>The question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>What I did meanwhile</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Why I did not just decide</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>The cash row inside CASH: "Vanguard — sweep cash", or the account's real name with "cash in this account" beneath it?</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Kept the real account name</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>The mock's shorter name is friendlier; the built one is traceable to an actual account you can open.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Keep the real account name</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>DONE — no code change; the mock was corrected to match</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Inside INVESTMENTS, order the categories biggest-first (the mock) or by liquidity (the rule approved in the pre-48 audit)?</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Kept liquidity order — the approved rule</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Changing an approved ordering rule on the strength of one drawing is how rules quietly die.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Biggest first</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>DONE — bar and list both sort by size; supersedes the liquidity rule, logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>The "This month's cash flow" row and the "＋ Add or connect an account" button sit below the cushion. Neither is in the mock. Keep or drop?</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Kept both</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>They are approved features and the add button is this screen's only way to add an account.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Keep add or connect. Delete cashflow.</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>DONE — the row and its code are gone; the button stays</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Should the By category / By institution buttons appear on the first-day screen?</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Left them off until there is an account</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>On an empty screen the second button changes nothing — a dead control on the first screen a new person sees.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Yes, as it will give user view of what they can do in the app</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>DONE — both buttons show; By institution says what it will hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>The handoff turns the whole hero into a solid green block. Keep your approved white hero card?</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Kept your approved hero</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>v1 in the mock folder shows the handoff version to compare.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Keep the white hero card with green band</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>DONE — no change</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>The handoff adds a composition bar under WHAT YOU OWE and a progress bar in the cushion. Neither is in the approved MoneyKeel mocks.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Did not add either</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>They are new chart furniture, not corrections — worth a look before they go in.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>add both. Bar replaces donut.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>DONE — donut removed; assets bar, debts bar and cushion bar built</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
